--- a/testdata/realdata/manholes.xlsx
+++ b/testdata/realdata/manholes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>经纬度</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +474,11 @@
           <t>126.35658,45.84836</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +506,11 @@
           <t>125.49054,46.28308</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +538,11 @@
           <t>126.80521,45.6646</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,6 +570,11 @@
           <t>127.93067,45.14516</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -577,6 +602,11 @@
           <t>126.90518,45.75405</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -604,6 +634,11 @@
           <t>128.43826,45.77205</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -631,6 +666,11 @@
           <t>130.4355,46.6143</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -658,6 +698,11 @@
           <t>130.85679,45.92538</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -685,6 +730,11 @@
           <t>124.33964,47.71083</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -712,6 +762,11 @@
           <t>125.1941,48.93366</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -739,6 +794,11 @@
           <t>124.32176,51.04825</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -766,6 +826,11 @@
           <t>123.256,52.75869</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -793,6 +858,11 @@
           <t>126.73932,46.05659</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -818,6 +888,11 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>128.02084,46.78795</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>在网</t>
         </is>
       </c>
     </row>
